--- a/raw-data/VFT Compiled data 2025/GSP-BI-25-all.xlsx
+++ b/raw-data/VFT Compiled data 2025/GSP-BI-25-all.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\VFT\VFT_github\zyao78VFTcode\raw-data\VFT Compiled data 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55311EE4-3D94-4B25-A334-F0A5933E12CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B30E1F0B-C1CE-46FE-9EC4-DBEB00CDA9D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="22943" yWindow="1365" windowWidth="20715" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="-83" yWindow="0" windowWidth="11686" windowHeight="13763" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GSP-BI-East" sheetId="1" r:id="rId1"/>
